--- a/e2e/data/test-data-salary-deduction.xlsx
+++ b/e2e/data/test-data-salary-deduction.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,9 +430,12 @@
         <v>dplkEmployer</v>
       </c>
       <c r="J1" t="str">
+        <v>Potongan lain - lain</v>
+      </c>
+      <c r="K1" t="str">
         <v>totalExpected</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>totalEmployerExpected</v>
       </c>
     </row>
@@ -465,9 +468,12 @@
         <v>100000</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2">
         <v>5</v>
       </c>
     </row>
@@ -500,9 +506,12 @@
         <v>100000</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>100000</v>
       </c>
       <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
         <v>5</v>
       </c>
     </row>
@@ -534,10 +543,13 @@
       <c r="I4">
         <v>100000</v>
       </c>
-      <c r="J4">
-        <v>35</v>
+      <c r="J4" t="str">
+        <v/>
       </c>
       <c r="K4">
+        <v>40</v>
+      </c>
+      <c r="L4">
         <v>5</v>
       </c>
     </row>
@@ -570,9 +582,12 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -604,24 +619,26 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <v>25</v>
+      <c r="J6" t="str">
+        <v/>
       </c>
       <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,15 +672,18 @@
         <v>employee13Seguranca</v>
       </c>
       <c r="K1" t="str">
+        <v>Potongan lain - lain</v>
+      </c>
+      <c r="L1" t="str">
         <v>totalExpected</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>employerSeguranca</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>employer13Seguranca</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>totalEmployerExpected</v>
       </c>
     </row>
@@ -699,15 +719,18 @@
         <v>50</v>
       </c>
       <c r="K2">
-        <v>1650</v>
+        <v>50</v>
       </c>
       <c r="L2">
+        <v>1700</v>
+      </c>
+      <c r="M2">
         <v>200</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>60</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>260</v>
       </c>
     </row>
@@ -743,15 +766,18 @@
         <v>50</v>
       </c>
       <c r="K3">
-        <v>2650</v>
+        <v>50</v>
       </c>
       <c r="L3">
+        <v>2700</v>
+      </c>
+      <c r="M3">
         <v>200</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>60</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>260</v>
       </c>
     </row>
@@ -786,16 +812,19 @@
       <c r="J4">
         <v>50</v>
       </c>
-      <c r="K4">
-        <v>2650</v>
+      <c r="K4" t="str">
+        <v/>
       </c>
       <c r="L4">
+        <v>2700</v>
+      </c>
+      <c r="M4">
         <v>200</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>60</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>260</v>
       </c>
     </row>
@@ -831,15 +860,18 @@
         <v>50</v>
       </c>
       <c r="K5">
-        <v>1650</v>
+        <v>50</v>
       </c>
       <c r="L5">
+        <v>1700</v>
+      </c>
+      <c r="M5">
         <v>200</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>60</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>260</v>
       </c>
     </row>
@@ -874,23 +906,25 @@
       <c r="J6">
         <v>50</v>
       </c>
-      <c r="K6">
-        <v>1650</v>
+      <c r="K6" t="str">
+        <v/>
       </c>
       <c r="L6">
+        <v>1700</v>
+      </c>
+      <c r="M6">
         <v>200</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>60</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>260</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/e2e/data/test-data-salary-deduction.xlsx
+++ b/e2e/data/test-data-salary-deduction.xlsx
@@ -1,43 +1,213 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Telkomcel\coding\test\e2e\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82E78C5-8FE7-436F-870F-4C55AC098AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="11895" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Homestaff" sheetId="1" r:id="rId1"/>
     <sheet name="ExpatLocal" sheetId="2" r:id="rId2"/>
     <sheet name="DeductionTransfer" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>employee</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>mandatory</t>
+  </si>
+  <si>
+    <t>pension</t>
+  </si>
+  <si>
+    <t>dplkEmployer</t>
+  </si>
+  <si>
+    <t>Potongan Iuran Koperasi</t>
+  </si>
+  <si>
+    <t>Potongan lain - lain</t>
+  </si>
+  <si>
+    <t>totalExpected</t>
+  </si>
+  <si>
+    <t>totalEmployerExpected</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>zakat</t>
+  </si>
+  <si>
+    <t>employeeDeduction</t>
+  </si>
+  <si>
+    <t>employeeSeguranca</t>
+  </si>
+  <si>
+    <t>employee13Seguranca</t>
+  </si>
+  <si>
+    <t>employerSeguranca</t>
+  </si>
+  <si>
+    <t>employer13Seguranca</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>deductionType</t>
+  </si>
+  <si>
+    <t>transferTo</t>
+  </si>
+  <si>
+    <t>transferToLabel</t>
+  </si>
+  <si>
+    <t>bankName</t>
+  </si>
+  <si>
+    <t>accountNumber</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>Zakat Deduction</t>
+  </si>
+  <si>
+    <t>PT AZKO</t>
+  </si>
+  <si>
+    <t>[Company] PT AZKO - Mandiri</t>
+  </si>
+  <si>
+    <t>Mandiri</t>
+  </si>
+  <si>
+    <t>928379837</t>
+  </si>
+  <si>
+    <t>TWP Deduction</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>IDP Deduction</t>
+  </si>
+  <si>
+    <t>Heri Mulyadi</t>
+  </si>
+  <si>
+    <t>[Personal] Heri Mulyadi - BCA</t>
+  </si>
+  <si>
+    <t>BCA</t>
+  </si>
+  <si>
+    <t>233643546</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,14 +236,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,62 +577,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>employee</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>period</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rate</v>
-      </c>
-      <c r="G1" t="str">
-        <v>mandatory</v>
-      </c>
-      <c r="H1" t="str">
-        <v>pension</v>
-      </c>
-      <c r="I1" t="str">
-        <v>dplkEmployer</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Potongan lain - lain</v>
-      </c>
-      <c r="K1" t="str">
-        <v>totalExpected</v>
-      </c>
-      <c r="L1" t="str">
-        <v>totalEmployerExpected</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-01</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -471,27 +657,30 @@
         <v>100000</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>100000</v>
       </c>
       <c r="L2">
+        <v>35</v>
+      </c>
+      <c r="M2">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-01</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -509,199 +698,205 @@
         <v>100000</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>100000</v>
       </c>
       <c r="L3">
+        <v>45</v>
+      </c>
+      <c r="M3">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-01</v>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20000</v>
       </c>
       <c r="G4">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="H4">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>100000</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
       <c r="K4">
-        <v>40</v>
+        <v>100000</v>
       </c>
       <c r="L4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>35</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
       </c>
       <c r="F5">
         <v>20000</v>
       </c>
       <c r="G5">
-        <v>500000</v>
+        <v>35000</v>
       </c>
       <c r="H5">
+        <v>10000</v>
+      </c>
+      <c r="I5">
+        <v>24000</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>100000</v>
-      </c>
       <c r="K5">
-        <v>30</v>
+        <v>42000</v>
       </c>
       <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5.55</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
       </c>
       <c r="F6">
         <v>20000</v>
       </c>
       <c r="G6">
-        <v>500000</v>
+        <v>26000</v>
       </c>
       <c r="H6">
+        <v>15000</v>
+      </c>
+      <c r="I6">
+        <v>38000</v>
+      </c>
+      <c r="J6">
+        <v>20500</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6">
-        <v>30</v>
-      </c>
       <c r="L6">
-        <v>0</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError sqref="A1:M3 B4:M4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>employee</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>period</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rate</v>
-      </c>
-      <c r="G1" t="str">
-        <v>zakat</v>
-      </c>
-      <c r="H1" t="str">
-        <v>employeeDeduction</v>
-      </c>
-      <c r="I1" t="str">
-        <v>employeeSeguranca</v>
-      </c>
-      <c r="J1" t="str">
-        <v>employee13Seguranca</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Potongan lain - lain</v>
-      </c>
-      <c r="L1" t="str">
-        <v>totalExpected</v>
-      </c>
-      <c r="M1" t="str">
-        <v>employerSeguranca</v>
-      </c>
-      <c r="N1" t="str">
-        <v>employer13Seguranca</v>
-      </c>
-      <c r="O1" t="str">
-        <v>totalEmployerExpected</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-02</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -722,33 +917,36 @@
         <v>50</v>
       </c>
       <c r="L2">
-        <v>1700</v>
+        <v>50</v>
       </c>
       <c r="M2">
+        <v>1750</v>
+      </c>
+      <c r="N2">
         <v>200</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>60</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>260</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-02</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -769,33 +967,36 @@
         <v>50</v>
       </c>
       <c r="L3">
-        <v>2700</v>
+        <v>50</v>
       </c>
       <c r="M3">
+        <v>2750</v>
+      </c>
+      <c r="N3">
         <v>200</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>60</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>260</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C4" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-02</v>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20000</v>
@@ -804,7 +1005,7 @@
         <v>500</v>
       </c>
       <c r="H4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -812,304 +1013,420 @@
       <c r="J4">
         <v>50</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="K4">
+        <v>50</v>
       </c>
       <c r="L4">
-        <v>2700</v>
+        <v>50</v>
       </c>
       <c r="M4">
+        <v>1750</v>
+      </c>
+      <c r="N4">
         <v>200</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>60</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>260</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
       </c>
       <c r="F5">
         <v>20000</v>
       </c>
-      <c r="G5">
-        <v>500</v>
-      </c>
-      <c r="H5">
-        <v>1000</v>
-      </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
       <c r="K5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>1700</v>
-      </c>
-      <c r="M5">
-        <v>200</v>
-      </c>
-      <c r="N5">
-        <v>60</v>
-      </c>
-      <c r="O5">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>20</v>
+      </c>
+      <c r="M5" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="P5" s="1">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C6" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
       </c>
       <c r="F6">
         <v>20000</v>
       </c>
-      <c r="G6">
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="P6" s="1">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>20000</v>
+      </c>
+      <c r="K7">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="P7" s="1">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>20000</v>
+      </c>
+      <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8" s="1">
+        <v>12</v>
+      </c>
+      <c r="P8" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>20000</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="P9" s="1">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>20000</v>
+      </c>
+      <c r="K10">
+        <v>60</v>
+      </c>
+      <c r="L10">
+        <v>20</v>
+      </c>
+      <c r="M10" s="1">
+        <v>42</v>
+      </c>
+      <c r="P10" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>20000</v>
+      </c>
+      <c r="G11">
         <v>500</v>
       </c>
-      <c r="H6">
+      <c r="H11">
         <v>1000</v>
       </c>
-      <c r="I6">
+      <c r="I11">
         <v>100</v>
       </c>
-      <c r="J6">
+      <c r="J11">
         <v>50</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
-        <v>1700</v>
-      </c>
-      <c r="M6">
+      <c r="K11">
+        <v>50</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>1750</v>
+      </c>
+      <c r="N11">
         <v>200</v>
       </c>
-      <c r="N6">
+      <c r="O11">
         <v>60</v>
       </c>
-      <c r="O6">
+      <c r="P11">
         <v>260</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError sqref="A1:P3 B4:P4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>period</v>
-      </c>
-      <c r="D1" t="str">
-        <v>deductionType</v>
-      </c>
-      <c r="E1" t="str">
-        <v>transferTo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>transferToLabel</v>
-      </c>
-      <c r="G1" t="str">
-        <v>bankName</v>
-      </c>
-      <c r="H1" t="str">
-        <v>accountNumber</v>
-      </c>
-      <c r="I1" t="str">
-        <v>amount</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Zakat Deduction</v>
-      </c>
-      <c r="E2" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F2" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H2" t="str">
-        <v>928379837</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D3" t="str">
-        <v>TWP Deduction</v>
-      </c>
-      <c r="E3" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F3" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H3" t="str">
-        <v>928379837</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D4" t="str">
-        <v>TWP Deduction</v>
-      </c>
-      <c r="E4" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F4" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H4" t="str">
-        <v>928379837</v>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2026-09</v>
-      </c>
-      <c r="D5" t="str">
-        <v>IDP Deduction</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Heri Mulyadi</v>
-      </c>
-      <c r="F5" t="str">
-        <v>[Personal] Heri Mulyadi - BCA</v>
-      </c>
-      <c r="G5" t="str">
-        <v>BCA</v>
-      </c>
-      <c r="H5" t="str">
-        <v>233643546</v>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-09</v>
-      </c>
-      <c r="D6" t="str">
-        <v>IDP Deduction</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Heri Mulyadi</v>
-      </c>
-      <c r="F6" t="str">
-        <v>[Personal] Heri Mulyadi - BCA</v>
-      </c>
-      <c r="G6" t="str">
-        <v>BCA</v>
-      </c>
-      <c r="H6" t="str">
-        <v>233643546</v>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError sqref="A1:I6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/e2e/data/test-data-salary-deduction.xlsx
+++ b/e2e/data/test-data-salary-deduction.xlsx
@@ -1,213 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Telkomcel\coding\test\e2e\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82E78C5-8FE7-436F-870F-4C55AC098AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="11895" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Homestaff" sheetId="1" r:id="rId1"/>
     <sheet name="ExpatLocal" sheetId="2" r:id="rId2"/>
     <sheet name="DeductionTransfer" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>employee</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>mandatory</t>
-  </si>
-  <si>
-    <t>pension</t>
-  </si>
-  <si>
-    <t>dplkEmployer</t>
-  </si>
-  <si>
-    <t>Potongan Iuran Koperasi</t>
-  </si>
-  <si>
-    <t>Potongan lain - lain</t>
-  </si>
-  <si>
-    <t>totalExpected</t>
-  </si>
-  <si>
-    <t>totalEmployerExpected</t>
-  </si>
-  <si>
-    <t>Add</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>2026-01</t>
-  </si>
-  <si>
-    <t>Edit</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>zakat</t>
-  </si>
-  <si>
-    <t>employeeDeduction</t>
-  </si>
-  <si>
-    <t>employeeSeguranca</t>
-  </si>
-  <si>
-    <t>employee13Seguranca</t>
-  </si>
-  <si>
-    <t>employerSeguranca</t>
-  </si>
-  <si>
-    <t>employer13Seguranca</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>2026-02</t>
-  </si>
-  <si>
-    <t>deductionType</t>
-  </si>
-  <si>
-    <t>transferTo</t>
-  </si>
-  <si>
-    <t>transferToLabel</t>
-  </si>
-  <si>
-    <t>bankName</t>
-  </si>
-  <si>
-    <t>accountNumber</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>Zakat Deduction</t>
-  </si>
-  <si>
-    <t>PT AZKO</t>
-  </si>
-  <si>
-    <t>[Company] PT AZKO - Mandiri</t>
-  </si>
-  <si>
-    <t>Mandiri</t>
-  </si>
-  <si>
-    <t>928379837</t>
-  </si>
-  <si>
-    <t>TWP Deduction</t>
-  </si>
-  <si>
-    <t>Delete</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>IDP Deduction</t>
-  </si>
-  <si>
-    <t>Heri Mulyadi</t>
-  </si>
-  <si>
-    <t>[Personal] Heri Mulyadi - BCA</t>
-  </si>
-  <si>
-    <t>BCA</t>
-  </si>
-  <si>
-    <t>233643546</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -236,23 +66,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -577,69 +398,65 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>action</v>
+      </c>
+      <c r="C1" t="str">
+        <v>employee</v>
+      </c>
+      <c r="D1" t="str">
+        <v>category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>period</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>mandatory</v>
+      </c>
+      <c r="H1" t="str">
+        <v>pension</v>
+      </c>
+      <c r="I1" t="str">
+        <v>dplkEmployer</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Potongan Iuran Koperasi</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Potongan lain - lain</v>
+      </c>
+      <c r="L1" t="str">
+        <v>totalExpected</v>
+      </c>
+      <c r="M1" t="str">
+        <v>totalEmployerExpected</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
+      <c r="B2" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Lestari Putri Cantika</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Homestaff</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-01</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -666,21 +483,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
+      <c r="B3" t="str">
+        <v>Edit</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Lestari Putri Cantika</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Homestaff</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-01</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -707,21 +524,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
+      <c r="B4" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Lestari Putri Cantika</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Homestaff</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4">
         <v>20000</v>
@@ -748,15 +565,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
+      <c r="B5" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C5" t="str">
+        <v>HERU YULIANTO</v>
       </c>
       <c r="F5">
         <v>20000</v>
@@ -777,21 +594,21 @@
         <v>42000</v>
       </c>
       <c r="L5">
-        <v>5.55</v>
+        <v>4.35</v>
       </c>
       <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
+      <c r="B6" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SYALDY KHARISMA ANANDA</v>
       </c>
       <c r="F6">
         <v>20000</v>
@@ -812,91 +629,88 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4.9800000000000004</v>
+        <v>3.08</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M3 B4:M4" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>action</v>
+      </c>
+      <c r="C1" t="str">
+        <v>employee</v>
+      </c>
+      <c r="D1" t="str">
+        <v>category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>period</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>zakat</v>
+      </c>
+      <c r="H1" t="str">
+        <v>employeeDeduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>employeeSeguranca</v>
+      </c>
+      <c r="J1" t="str">
+        <v>employee13Seguranca</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Potongan Iuran Koperasi</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Potongan lain - lain</v>
+      </c>
+      <c r="M1" t="str">
+        <v>totalExpected</v>
+      </c>
+      <c r="N1" t="str">
+        <v>employerSeguranca</v>
+      </c>
+      <c r="O1" t="str">
+        <v>employer13Seguranca</v>
+      </c>
+      <c r="P1" t="str">
+        <v>totalEmployerExpected</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
+      <c r="B2" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C2" t="str">
+        <v>AGOSTINHO GOMES FERNANDES</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Expat</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-02</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -932,21 +746,21 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
+      <c r="B3" t="str">
+        <v>Edit</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AGOSTINHO GOMES FERNANDES</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Expat</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-02</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -982,21 +796,21 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
+      <c r="B4" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AGOSTINHO GOMES FERNANDES</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Expat</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4">
         <v>20000</v>
@@ -1032,15 +846,15 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
+      <c r="B5" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ADROALDINO DA SILVA NORONHA TOME</v>
       </c>
       <c r="F5">
         <v>20000</v>
@@ -1051,22 +865,22 @@
       <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5">
         <v>7.2</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5">
         <v>10.8</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
+      <c r="B6" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CELIA MARIA REGO DE FATIMA</v>
       </c>
       <c r="F6">
         <v>20000</v>
@@ -1077,22 +891,22 @@
       <c r="L6">
         <v>20</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6">
         <v>13.6</v>
       </c>
-      <c r="P6" s="1">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
+      <c r="B7" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CLAUDIO DA COSTA ALVES</v>
       </c>
       <c r="F7">
         <v>20000</v>
@@ -1103,22 +917,22 @@
       <c r="L7">
         <v>20</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7">
         <v>8.4</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7">
         <v>12.6</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
+      <c r="B8" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C8" t="str">
+        <v>DIAN EVIYANTI APLUGI</v>
       </c>
       <c r="F8">
         <v>20000</v>
@@ -1129,22 +943,22 @@
       <c r="L8">
         <v>20</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8">
         <v>12</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
+      <c r="B9" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C9" t="str">
+        <v>AHMAD RIYANA SAPUTRA</v>
       </c>
       <c r="F9">
         <v>20000</v>
@@ -1155,22 +969,22 @@
       <c r="L9">
         <v>20</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9">
         <v>20.8</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9">
         <v>31.2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
+      <c r="B10" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C10" t="str">
+        <v>RIMBUN SIBURIAN</v>
       </c>
       <c r="F10">
         <v>20000</v>
@@ -1181,25 +995,25 @@
       <c r="L10">
         <v>20</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10">
         <v>42</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
+      <c r="B11" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C11" t="str">
+        <v>RIMBUN SIBURIAN</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-01</v>
       </c>
       <c r="F11">
         <v>20000</v>
@@ -1237,187 +1051,185 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P3 B4:P4" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>action</v>
+      </c>
+      <c r="C1" t="str">
+        <v>period</v>
+      </c>
+      <c r="D1" t="str">
+        <v>deductionType</v>
+      </c>
+      <c r="E1" t="str">
+        <v>transferTo</v>
+      </c>
+      <c r="F1" t="str">
+        <v>transferToLabel</v>
+      </c>
+      <c r="G1" t="str">
+        <v>bankName</v>
+      </c>
+      <c r="H1" t="str">
+        <v>accountNumber</v>
+      </c>
+      <c r="I1" t="str">
+        <v>amount</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" t="s">
-        <v>39</v>
+      <c r="B2" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Zakat Deduction</v>
+      </c>
+      <c r="E2" t="str">
+        <v>PT AZKO</v>
+      </c>
+      <c r="F2" t="str">
+        <v>[Company] PT AZKO - Mandiri</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Mandiri</v>
+      </c>
+      <c r="H2" t="str">
+        <v>928379837</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
+      <c r="B3" t="str">
+        <v>Edit</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TWP Deduction</v>
+      </c>
+      <c r="E3" t="str">
+        <v>PT AZKO</v>
+      </c>
+      <c r="F3" t="str">
+        <v>[Company] PT AZKO - Mandiri</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mandiri</v>
+      </c>
+      <c r="H3" t="str">
+        <v>928379837</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
+      <c r="B4" t="str">
+        <v>Delete</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TWP Deduction</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PT AZKO</v>
+      </c>
+      <c r="F4" t="str">
+        <v>[Company] PT AZKO - Mandiri</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Mandiri</v>
+      </c>
+      <c r="H4" t="str">
+        <v>928379837</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>47</v>
+      <c r="B5" t="str">
+        <v>Add</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-09</v>
+      </c>
+      <c r="D5" t="str">
+        <v>IDP Deduction</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Heri Mulyadi</v>
+      </c>
+      <c r="F5" t="str">
+        <v>[Personal] Heri Mulyadi - BCA</v>
+      </c>
+      <c r="G5" t="str">
+        <v>BCA</v>
+      </c>
+      <c r="H5" t="str">
+        <v>233643546</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
+      <c r="B6" t="str">
+        <v>Delete</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-09</v>
+      </c>
+      <c r="D6" t="str">
+        <v>IDP Deduction</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Heri Mulyadi</v>
+      </c>
+      <c r="F6" t="str">
+        <v>[Personal] Heri Mulyadi - BCA</v>
+      </c>
+      <c r="G6" t="str">
+        <v>BCA</v>
+      </c>
+      <c r="H6" t="str">
+        <v>233643546</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1426,7 +1238,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I6" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/e2e/data/test-data-salary-deduction.xlsx
+++ b/e2e/data/test-data-salary-deduction.xlsx
@@ -1,43 +1,199 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Telkomcel\coding\test\e2e\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E3038-55E1-4E0C-A804-55FF9BBE6738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Homestaff" sheetId="1" r:id="rId1"/>
     <sheet name="ExpatLocal" sheetId="2" r:id="rId2"/>
     <sheet name="DeductionTransfer" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>employee</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>mandatory</t>
+  </si>
+  <si>
+    <t>pension</t>
+  </si>
+  <si>
+    <t>dplkEmployer</t>
+  </si>
+  <si>
+    <t>Potongan Iuran Koperasi</t>
+  </si>
+  <si>
+    <t>Potongan lain - lain</t>
+  </si>
+  <si>
+    <t>totalExpected</t>
+  </si>
+  <si>
+    <t>totalEmployerExpected</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>zakat</t>
+  </si>
+  <si>
+    <t>employeeDeduction</t>
+  </si>
+  <si>
+    <t>employeeSeguranca</t>
+  </si>
+  <si>
+    <t>employee13Seguranca</t>
+  </si>
+  <si>
+    <t>employerSeguranca</t>
+  </si>
+  <si>
+    <t>employer13Seguranca</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>deductionType</t>
+  </si>
+  <si>
+    <t>transferTo</t>
+  </si>
+  <si>
+    <t>transferToLabel</t>
+  </si>
+  <si>
+    <t>bankName</t>
+  </si>
+  <si>
+    <t>accountNumber</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>Zakat Deduction</t>
+  </si>
+  <si>
+    <t>PT AZKO</t>
+  </si>
+  <si>
+    <t>[Company] PT AZKO - Mandiri</t>
+  </si>
+  <si>
+    <t>Mandiri</t>
+  </si>
+  <si>
+    <t>928379837</t>
+  </si>
+  <si>
+    <t>TWP Deduction</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>IDP Deduction</t>
+  </si>
+  <si>
+    <t>Heri Mulyadi</t>
+  </si>
+  <si>
+    <t>[Personal] Heri Mulyadi - BCA</t>
+  </si>
+  <si>
+    <t>BCA</t>
+  </si>
+  <si>
+    <t>233643546</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,13 +223,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,65 +562,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>employee</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>period</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rate</v>
-      </c>
-      <c r="G1" t="str">
-        <v>mandatory</v>
-      </c>
-      <c r="H1" t="str">
-        <v>pension</v>
-      </c>
-      <c r="I1" t="str">
-        <v>dplkEmployer</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Potongan Iuran Koperasi</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Potongan lain - lain</v>
-      </c>
-      <c r="L1" t="str">
-        <v>totalExpected</v>
-      </c>
-      <c r="M1" t="str">
-        <v>totalEmployerExpected</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-01</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -483,21 +648,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-01</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -524,21 +689,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Lestari Putri Cantika</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Homestaff</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20000</v>
@@ -565,15 +730,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>HERU YULIANTO</v>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
       <c r="F5">
         <v>20000</v>
@@ -594,21 +759,21 @@
         <v>42000</v>
       </c>
       <c r="L5">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M5">
         <v>1.2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C6" t="str">
-        <v>SYALDY KHARISMA ANANDA</v>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
       </c>
       <c r="F6">
         <v>20000</v>
@@ -636,81 +801,83 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError sqref="A1:M6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>employee</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>period</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rate</v>
-      </c>
-      <c r="G1" t="str">
-        <v>zakat</v>
-      </c>
-      <c r="H1" t="str">
-        <v>employeeDeduction</v>
-      </c>
-      <c r="I1" t="str">
-        <v>employeeSeguranca</v>
-      </c>
-      <c r="J1" t="str">
-        <v>employee13Seguranca</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Potongan Iuran Koperasi</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Potongan lain - lain</v>
-      </c>
-      <c r="M1" t="str">
-        <v>totalExpected</v>
-      </c>
-      <c r="N1" t="str">
-        <v>employerSeguranca</v>
-      </c>
-      <c r="O1" t="str">
-        <v>employer13Seguranca</v>
-      </c>
-      <c r="P1" t="str">
-        <v>totalEmployerExpected</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-02</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
       </c>
       <c r="F2">
         <v>20000</v>
@@ -746,21 +913,21 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-02</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -796,21 +963,21 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C4" t="str">
-        <v>AGOSTINHO GOMES FERNANDES</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Expat</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20000</v>
@@ -846,15 +1013,15 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>ADROALDINO DA SILVA NORONHA TOME</v>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
       </c>
       <c r="F5">
         <v>20000</v>
@@ -866,21 +1033,21 @@
         <v>20</v>
       </c>
       <c r="M5">
-        <v>7.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="P5">
         <v>10.8</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C6" t="str">
-        <v>CELIA MARIA REGO DE FATIMA</v>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
       </c>
       <c r="F6">
         <v>20000</v>
@@ -892,21 +1059,21 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>13.6</v>
+        <v>53.6</v>
       </c>
       <c r="P6">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C7" t="str">
-        <v>CLAUDIO DA COSTA ALVES</v>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
       </c>
       <c r="F7">
         <v>20000</v>
@@ -918,21 +1085,21 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>8.4</v>
+        <v>58.4</v>
       </c>
       <c r="P7">
         <v>12.6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C8" t="str">
-        <v>DIAN EVIYANTI APLUGI</v>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
       </c>
       <c r="F8">
         <v>20000</v>
@@ -944,21 +1111,21 @@
         <v>20</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="P8">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C9" t="str">
-        <v>AHMAD RIYANA SAPUTRA</v>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
       </c>
       <c r="F9">
         <v>20000</v>
@@ -970,21 +1137,21 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>20.8</v>
+        <v>90.8</v>
       </c>
       <c r="P9">
         <v>31.2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C10" t="str">
-        <v>RIMBUN SIBURIAN</v>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
       </c>
       <c r="F10">
         <v>20000</v>
@@ -996,24 +1163,24 @@
         <v>20</v>
       </c>
       <c r="M10">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="P10">
         <v>63</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C11" t="str">
-        <v>RIMBUN SIBURIAN</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-01</v>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
       </c>
       <c r="F11">
         <v>20000</v>
@@ -1052,193 +1219,136 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError sqref="A1:P4 A11:P11 A10:L10 N10:P10 A9:L9 N9:P9 A8:L8 N8:P8 A7:L7 N7:P7 A6:L6 N6:P6 A5:L5 N5:P5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>period</v>
-      </c>
-      <c r="D1" t="str">
-        <v>deductionType</v>
-      </c>
-      <c r="E1" t="str">
-        <v>transferTo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>transferToLabel</v>
-      </c>
-      <c r="G1" t="str">
-        <v>bankName</v>
-      </c>
-      <c r="H1" t="str">
-        <v>accountNumber</v>
-      </c>
-      <c r="I1" t="str">
-        <v>amount</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Zakat Deduction</v>
-      </c>
-      <c r="E2" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F2" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H2" t="str">
-        <v>928379837</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Edit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D3" t="str">
-        <v>TWP Deduction</v>
-      </c>
-      <c r="E3" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F3" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H3" t="str">
-        <v>928379837</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2026-08</v>
-      </c>
-      <c r="D4" t="str">
-        <v>TWP Deduction</v>
-      </c>
-      <c r="E4" t="str">
-        <v>PT AZKO</v>
-      </c>
-      <c r="F4" t="str">
-        <v>[Company] PT AZKO - Mandiri</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="H4" t="str">
-        <v>928379837</v>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" t="s">
+        <v>54</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Add</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2026-09</v>
-      </c>
-      <c r="D5" t="str">
-        <v>IDP Deduction</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Heri Mulyadi</v>
-      </c>
-      <c r="F5" t="str">
-        <v>[Personal] Heri Mulyadi - BCA</v>
-      </c>
-      <c r="G5" t="str">
-        <v>BCA</v>
-      </c>
-      <c r="H5" t="str">
-        <v>233643546</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Delete</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-09</v>
-      </c>
-      <c r="D6" t="str">
-        <v>IDP Deduction</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Heri Mulyadi</v>
-      </c>
-      <c r="F6" t="str">
-        <v>[Personal] Heri Mulyadi - BCA</v>
-      </c>
-      <c r="G6" t="str">
-        <v>BCA</v>
-      </c>
-      <c r="H6" t="str">
-        <v>233643546</v>
-      </c>
-      <c r="I6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError sqref="A1:I3 B4:I4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/e2e/data/test-data-salary-deduction.xlsx
+++ b/e2e/data/test-data-salary-deduction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Telkomcel\coding\test\e2e\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E3038-55E1-4E0C-A804-55FF9BBE6738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E3B38-34F3-4C79-9B7D-F0CD629A474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2100" windowWidth="23775" windowHeight="10140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homestaff" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -150,9 +150,6 @@
     <t>amount</t>
   </si>
   <si>
-    <t>2026-08</t>
-  </si>
-  <si>
     <t>Zakat Deduction</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>TWP Deduction</t>
-  </si>
-  <si>
-    <t>2026-09</t>
   </si>
   <si>
     <t>IDP Deduction</t>
@@ -1266,22 +1260,22 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>44</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>45</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>46</v>
-      </c>
-      <c r="H2" t="s">
-        <v>47</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1295,22 +1289,22 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
         <v>44</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>45</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>46</v>
-      </c>
-      <c r="H3" t="s">
-        <v>47</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1324,22 +1318,22 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>52</v>
-      </c>
-      <c r="G4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>54</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1348,7 +1342,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I3 B4:I4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 B4 A3:B3 A2:B2 D2:I2 D3:I3 D4:I4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>